--- a/config/excel/CfgLootQualities.xlsx
+++ b/config/excel/CfgLootQualities.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CfgLootQualities" sheetId="1" r:id="R63e82c66956a4b68"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CfgLootQualities" sheetId="1" r:id="R618c09ee7b2f4109"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -13,7 +13,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="2">
+  <x:fonts count="5">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -23,13 +23,43 @@
       <x:sz val="11"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF0000FF"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="2">
+  <x:fills count="5">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="gray125"/>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDBEAF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
     </x:fill>
   </x:fills>
   <x:borders count="1">
@@ -38,9 +68,18 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="2">
+  <x:cellXfs count="9">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -249,383 +288,433 @@
     <x:col min="4" max="4" width="20" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" s="1" t="str">
+    <x:row r="1" ht="32" customHeight="1">
+      <x:c r="A1" s="4" t="str">
         <x:v>ID</x:v>
       </x:c>
-      <x:c r="B1" s="1" t="str">
+      <x:c r="B1" s="4" t="str">
         <x:v>PoolID</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="str">
+      <x:c r="C1" s="4" t="str">
         <x:v>Quality</x:v>
       </x:c>
-      <x:c r="D1" s="1" t="str">
+      <x:c r="D1" s="4" t="str">
         <x:v>Weight</x:v>
       </x:c>
     </x:row>
-    <x:row r="2">
-      <x:c r="A2" t="str">
+    <x:row r="2" ht="24" customHeight="1">
+      <x:c r="A2" s="5" t="str">
         <x:v>string</x:v>
       </x:c>
-      <x:c r="B2" t="str">
+      <x:c r="B2" s="5" t="str">
         <x:v>string</x:v>
       </x:c>
-      <x:c r="C2" t="str">
+      <x:c r="C2" s="5" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="D2" t="str">
+      <x:c r="D2" s="5" t="str">
         <x:v>int</x:v>
       </x:c>
     </x:row>
-    <x:row r="3">
-      <x:c r="A3" t="str">
+    <x:row r="3" ht="42" customHeight="1">
+      <x:c r="A3" s="7" t="str">
         <x:v># 池品质条目身份</x:v>
       </x:c>
-      <x:c r="B3" t="str">
+      <x:c r="B3" s="7" t="str">
         <x:v>掉落池身份</x:v>
       </x:c>
-      <x:c r="C3" t="str">
+      <x:c r="C3" s="7" t="str">
         <x:v>品质枚举值</x:v>
       </x:c>
-      <x:c r="D3" t="str">
+      <x:c r="D3" s="7" t="str">
         <x:v>抽取权重</x:v>
       </x:c>
     </x:row>
-    <x:row r="4">
-      <x:c r="A4" t="str">
+    <x:row r="4" ht="24" customHeight="1">
+      <x:c r="A4" s="8" t="str">
         <x:v>default_0</x:v>
       </x:c>
-      <x:c r="B4" t="str">
+      <x:c r="B4" s="8" t="str">
         <x:v>default</x:v>
       </x:c>
-      <x:c r="C4" t="n">
+      <x:c r="C4" s="8" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D4" t="n">
+      <x:c r="D4" s="8" t="n">
         <x:v>60</x:v>
       </x:c>
     </x:row>
-    <x:row r="5">
-      <x:c r="A5" t="str">
+    <x:row r="5" ht="24" customHeight="1">
+      <x:c r="A5" s="8" t="str">
         <x:v>default_1</x:v>
       </x:c>
-      <x:c r="B5" t="str">
+      <x:c r="B5" s="8" t="str">
         <x:v>default</x:v>
       </x:c>
-      <x:c r="C5" t="n">
+      <x:c r="C5" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D5" t="n">
+      <x:c r="D5" s="8" t="n">
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="6">
-      <x:c r="A6" t="str">
+    <x:row r="6" ht="24" customHeight="1">
+      <x:c r="A6" s="8" t="str">
         <x:v>default_2</x:v>
       </x:c>
-      <x:c r="B6" t="str">
+      <x:c r="B6" s="8" t="str">
         <x:v>default</x:v>
       </x:c>
-      <x:c r="C6" t="n">
+      <x:c r="C6" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D6" t="n">
+      <x:c r="D6" s="8" t="n">
         <x:v>10</x:v>
       </x:c>
     </x:row>
-    <x:row r="7">
-      <x:c r="A7" t="str">
+    <x:row r="7" ht="24" customHeight="1">
+      <x:c r="A7" s="8" t="str">
         <x:v>default_3</x:v>
       </x:c>
-      <x:c r="B7" t="str">
+      <x:c r="B7" s="8" t="str">
         <x:v>default</x:v>
       </x:c>
-      <x:c r="C7" t="n">
+      <x:c r="C7" s="8" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" t="n">
+      <x:c r="D7" s="8" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="8">
-      <x:c r="A8" t="str">
+    <x:row r="8" ht="24" customHeight="1">
+      <x:c r="A8" s="8" t="str">
         <x:v>default_4</x:v>
       </x:c>
-      <x:c r="B8" t="str">
+      <x:c r="B8" s="8" t="str">
         <x:v>default</x:v>
       </x:c>
-      <x:c r="C8" t="n">
+      <x:c r="C8" s="8" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D8" t="n">
+      <x:c r="D8" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="9">
-      <x:c r="A9" t="str">
+    <x:row r="9" ht="24" customHeight="1">
+      <x:c r="A9" s="8" t="str">
         <x:v>default_5</x:v>
       </x:c>
-      <x:c r="B9" t="str">
+      <x:c r="B9" s="8" t="str">
         <x:v>default</x:v>
       </x:c>
-      <x:c r="C9" t="n">
+      <x:c r="C9" s="8" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="D9" t="n">
+      <x:c r="D9" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="10">
-      <x:c r="A10" t="str">
+    <x:row r="10" ht="24" customHeight="1">
+      <x:c r="A10" s="8" t="str">
         <x:v>merchant_0</x:v>
       </x:c>
-      <x:c r="B10" t="str">
+      <x:c r="B10" s="8" t="str">
         <x:v>merchant</x:v>
       </x:c>
-      <x:c r="C10" t="n">
+      <x:c r="C10" s="8" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D10" t="n">
+      <x:c r="D10" s="8" t="n">
         <x:v>60</x:v>
       </x:c>
     </x:row>
-    <x:row r="11">
-      <x:c r="A11" t="str">
+    <x:row r="11" ht="24" customHeight="1">
+      <x:c r="A11" s="8" t="str">
         <x:v>merchant_1</x:v>
       </x:c>
-      <x:c r="B11" t="str">
+      <x:c r="B11" s="8" t="str">
         <x:v>merchant</x:v>
       </x:c>
-      <x:c r="C11" t="n">
+      <x:c r="C11" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D11" t="n">
+      <x:c r="D11" s="8" t="n">
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="12">
-      <x:c r="A12" t="str">
+    <x:row r="12" ht="24" customHeight="1">
+      <x:c r="A12" s="8" t="str">
         <x:v>merchant_2</x:v>
       </x:c>
-      <x:c r="B12" t="str">
+      <x:c r="B12" s="8" t="str">
         <x:v>merchant</x:v>
       </x:c>
-      <x:c r="C12" t="n">
+      <x:c r="C12" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D12" t="n">
+      <x:c r="D12" s="8" t="n">
         <x:v>10</x:v>
       </x:c>
     </x:row>
-    <x:row r="13">
-      <x:c r="A13" t="str">
+    <x:row r="13" ht="24" customHeight="1">
+      <x:c r="A13" s="8" t="str">
         <x:v>merchant_3</x:v>
       </x:c>
-      <x:c r="B13" t="str">
+      <x:c r="B13" s="8" t="str">
         <x:v>merchant</x:v>
       </x:c>
-      <x:c r="C13" t="n">
+      <x:c r="C13" s="8" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D13" t="n">
+      <x:c r="D13" s="8" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="14">
-      <x:c r="A14" t="str">
+    <x:row r="14" ht="24" customHeight="1">
+      <x:c r="A14" s="8" t="str">
         <x:v>merchant_4</x:v>
       </x:c>
-      <x:c r="B14" t="str">
+      <x:c r="B14" s="8" t="str">
         <x:v>merchant</x:v>
       </x:c>
-      <x:c r="C14" t="n">
+      <x:c r="C14" s="8" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D14" t="n">
+      <x:c r="D14" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="15">
-      <x:c r="A15" t="str">
+    <x:row r="15" ht="24" customHeight="1">
+      <x:c r="A15" s="8" t="str">
         <x:v>merchant_5</x:v>
       </x:c>
-      <x:c r="B15" t="str">
+      <x:c r="B15" s="8" t="str">
         <x:v>merchant</x:v>
       </x:c>
-      <x:c r="C15" t="n">
+      <x:c r="C15" s="8" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="D15" t="n">
+      <x:c r="D15" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="16">
-      <x:c r="A16" t="str">
+    <x:row r="16" ht="24" customHeight="1">
+      <x:c r="A16" s="8" t="str">
         <x:v>treasure_0</x:v>
       </x:c>
-      <x:c r="B16" t="str">
+      <x:c r="B16" s="8" t="str">
         <x:v>treasure</x:v>
       </x:c>
-      <x:c r="C16" t="n">
+      <x:c r="C16" s="8" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D16" t="n">
+      <x:c r="D16" s="8" t="n">
         <x:v>45</x:v>
       </x:c>
     </x:row>
-    <x:row r="17">
-      <x:c r="A17" t="str">
+    <x:row r="17" ht="24" customHeight="1">
+      <x:c r="A17" s="8" t="str">
         <x:v>treasure_1</x:v>
       </x:c>
-      <x:c r="B17" t="str">
+      <x:c r="B17" s="8" t="str">
         <x:v>treasure</x:v>
       </x:c>
-      <x:c r="C17" t="n">
+      <x:c r="C17" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D17" t="n">
+      <x:c r="D17" s="8" t="n">
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="18">
-      <x:c r="A18" t="str">
+    <x:row r="18" ht="24" customHeight="1">
+      <x:c r="A18" s="8" t="str">
         <x:v>treasure_2</x:v>
       </x:c>
-      <x:c r="B18" t="str">
+      <x:c r="B18" s="8" t="str">
         <x:v>treasure</x:v>
       </x:c>
-      <x:c r="C18" t="n">
+      <x:c r="C18" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D18" t="n">
+      <x:c r="D18" s="8" t="n">
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="19">
-      <x:c r="A19" t="str">
+    <x:row r="19" ht="24" customHeight="1">
+      <x:c r="A19" s="8" t="str">
         <x:v>treasure_3</x:v>
       </x:c>
-      <x:c r="B19" t="str">
+      <x:c r="B19" s="8" t="str">
         <x:v>treasure</x:v>
       </x:c>
-      <x:c r="C19" t="n">
+      <x:c r="C19" s="8" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D19" t="n">
+      <x:c r="D19" s="8" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
-    <x:row r="20">
-      <x:c r="A20" t="str">
+    <x:row r="20" ht="24" customHeight="1">
+      <x:c r="A20" s="8" t="str">
         <x:v>treasure_4</x:v>
       </x:c>
-      <x:c r="B20" t="str">
+      <x:c r="B20" s="8" t="str">
         <x:v>treasure</x:v>
       </x:c>
-      <x:c r="C20" t="n">
+      <x:c r="C20" s="8" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D20" t="n">
+      <x:c r="D20" s="8" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
-    <x:row r="21">
-      <x:c r="A21" t="str">
+    <x:row r="21" ht="24" customHeight="1">
+      <x:c r="A21" s="8" t="str">
         <x:v>treasure_5</x:v>
       </x:c>
-      <x:c r="B21" t="str">
+      <x:c r="B21" s="8" t="str">
         <x:v>treasure</x:v>
       </x:c>
-      <x:c r="C21" t="n">
+      <x:c r="C21" s="8" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="D21" t="n">
+      <x:c r="D21" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="22">
-      <x:c r="A22" t="str">
-        <x:v>boss_0</x:v>
-      </x:c>
-      <x:c r="B22" t="str">
-        <x:v>boss</x:v>
-      </x:c>
-      <x:c r="C22" t="n">
+    <x:row r="22" ht="24" customHeight="1">
+      <x:c r="A22" s="8" t="str">
+        <x:v>v2_boss_0</x:v>
+      </x:c>
+      <x:c r="B22" s="8" t="str">
+        <x:v>boss_equipment</x:v>
+      </x:c>
+      <x:c r="C22" s="8" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D22" t="n">
+      <x:c r="D22" s="8" t="n">
         <x:v>20</x:v>
       </x:c>
     </x:row>
-    <x:row r="23">
-      <x:c r="A23" t="str">
-        <x:v>boss_1</x:v>
-      </x:c>
-      <x:c r="B23" t="str">
-        <x:v>boss</x:v>
-      </x:c>
-      <x:c r="C23" t="n">
+    <x:row r="23" ht="24" customHeight="1">
+      <x:c r="A23" s="8" t="str">
+        <x:v>v2_boss_1</x:v>
+      </x:c>
+      <x:c r="B23" s="8" t="str">
+        <x:v>boss_equipment</x:v>
+      </x:c>
+      <x:c r="C23" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D23" t="n">
+      <x:c r="D23" s="8" t="n">
         <x:v>35</x:v>
       </x:c>
     </x:row>
-    <x:row r="24">
-      <x:c r="A24" t="str">
-        <x:v>boss_2</x:v>
-      </x:c>
-      <x:c r="B24" t="str">
-        <x:v>boss</x:v>
-      </x:c>
-      <x:c r="C24" t="n">
+    <x:row r="24" ht="24" customHeight="1">
+      <x:c r="A24" s="8" t="str">
+        <x:v>v2_boss_2</x:v>
+      </x:c>
+      <x:c r="B24" s="8" t="str">
+        <x:v>boss_equipment</x:v>
+      </x:c>
+      <x:c r="C24" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D24" t="n">
+      <x:c r="D24" s="8" t="n">
         <x:v>25</x:v>
       </x:c>
     </x:row>
-    <x:row r="25">
-      <x:c r="A25" t="str">
-        <x:v>boss_3</x:v>
-      </x:c>
-      <x:c r="B25" t="str">
-        <x:v>boss</x:v>
-      </x:c>
-      <x:c r="C25" t="n">
+    <x:row r="25" ht="24" customHeight="1">
+      <x:c r="A25" s="8" t="str">
+        <x:v>v2_boss_3</x:v>
+      </x:c>
+      <x:c r="B25" s="8" t="str">
+        <x:v>boss_equipment</x:v>
+      </x:c>
+      <x:c r="C25" s="8" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D25" t="n">
+      <x:c r="D25" s="8" t="n">
         <x:v>12</x:v>
       </x:c>
     </x:row>
-    <x:row r="26">
-      <x:c r="A26" t="str">
-        <x:v>boss_4</x:v>
-      </x:c>
-      <x:c r="B26" t="str">
-        <x:v>boss</x:v>
-      </x:c>
-      <x:c r="C26" t="n">
+    <x:row r="26" ht="24" customHeight="1">
+      <x:c r="A26" s="8" t="str">
+        <x:v>v2_boss_4</x:v>
+      </x:c>
+      <x:c r="B26" s="8" t="str">
+        <x:v>boss_equipment</x:v>
+      </x:c>
+      <x:c r="C26" s="8" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D26" t="n">
+      <x:c r="D26" s="8" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
-    <x:row r="27">
-      <x:c r="A27" t="str">
-        <x:v>boss_5</x:v>
-      </x:c>
-      <x:c r="B27" t="str">
-        <x:v>boss</x:v>
-      </x:c>
-      <x:c r="C27" t="n">
+    <x:row r="27" ht="24" customHeight="1">
+      <x:c r="A27" s="8" t="str">
+        <x:v>v2_boss_5</x:v>
+      </x:c>
+      <x:c r="B27" s="8" t="str">
+        <x:v>boss_equipment</x:v>
+      </x:c>
+      <x:c r="C27" s="8" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="D27" t="n">
+      <x:c r="D27" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
+    </x:row>
+    <x:row r="28" ht="24" customHeight="1">
+      <x:c r="A28" s="8" t="str">
+        <x:v>region_chest_2</x:v>
+      </x:c>
+      <x:c r="B28" s="8" t="str">
+        <x:v>region_chest</x:v>
+      </x:c>
+      <x:c r="C28" s="8" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D28" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="24" customHeight="1">
+      <x:c r="A29" s="8"/>
+      <x:c r="B29" s="8"/>
+      <x:c r="C29" s="8"/>
+      <x:c r="D29" s="8"/>
+    </x:row>
+    <x:row r="30" ht="24" customHeight="1">
+      <x:c r="A30" s="8"/>
+      <x:c r="B30" s="8"/>
+      <x:c r="C30" s="8"/>
+      <x:c r="D30" s="8"/>
+    </x:row>
+    <x:row r="31" ht="24" customHeight="1">
+      <x:c r="A31" s="8"/>
+      <x:c r="B31" s="8"/>
+      <x:c r="C31" s="8"/>
+      <x:c r="D31" s="8"/>
+    </x:row>
+    <x:row r="32" ht="24" customHeight="1">
+      <x:c r="A32" s="8"/>
+      <x:c r="B32" s="8"/>
+      <x:c r="C32" s="8"/>
+      <x:c r="D32" s="8"/>
+    </x:row>
+    <x:row r="33" ht="24" customHeight="1">
+      <x:c r="A33" s="8"/>
+      <x:c r="B33" s="8"/>
+      <x:c r="C33" s="8"/>
+      <x:c r="D33" s="8"/>
+    </x:row>
+    <x:row r="34" ht="24" customHeight="1">
+      <x:c r="A34" s="8"/>
+      <x:c r="B34" s="8"/>
+      <x:c r="C34" s="8"/>
+      <x:c r="D34" s="8"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
